--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.7639,0.0083,0.0479,0.1300</t>
-  </si>
-  <si>
-    <t>0.0348,0.0104,0.0015,0.9858</t>
-  </si>
-  <si>
-    <t>0.5539,0.0635,0.0058,0.3171</t>
-  </si>
-  <si>
-    <t>0.0759,0.0077,0.0057,0.9679</t>
-  </si>
-  <si>
-    <t>0.9969,0.0019,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0010,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9817,0.0305,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9957,0.0017,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9899,0.0016,0.0001,0.0021</t>
-  </si>
-  <si>
-    <t>0.9951,0.0033,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9958,0.0017,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9943,0.0009,0.0000,0.0009</t>
-  </si>
-  <si>
-    <t>0.8734,0.1190,0.0114,0.0039</t>
-  </si>
-  <si>
-    <t>0.1099,0.0187,0.9102,0.0008</t>
-  </si>
-  <si>
-    <t>0.1151,0.0289,0.9086,0.0022</t>
-  </si>
-  <si>
-    <t>0.1817,0.0807,0.7190,0.0133</t>
-  </si>
-  <si>
-    <t>0.7092,0.1284,0.2263,0.0096</t>
-  </si>
-  <si>
-    <t>0.0038,0.9909,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.0449,0.9557,0.0048,0.0008</t>
-  </si>
-  <si>
-    <t>0.3025,0.7693,0.0155,0.0013</t>
-  </si>
-  <si>
-    <t>0.0184,0.9757,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.0068,0.9890,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.1155,0.0075,0.8783,0.0387</t>
-  </si>
-  <si>
-    <t>0.7469,0.0147,0.3146,0.0167</t>
-  </si>
-  <si>
-    <t>0.0481,0.0098,0.9521,0.0028</t>
-  </si>
-  <si>
-    <t>0.3505,0.0057,0.8137,0.0038</t>
-  </si>
-  <si>
-    <t>0.1149,0.0110,0.9263,0.0046</t>
-  </si>
-  <si>
-    <t>0.1380,0.0104,0.8891,0.0046</t>
-  </si>
-  <si>
-    <t>0.0045,0.0016,0.9857,0.0212</t>
-  </si>
-  <si>
-    <t>0.6801,0.4019,0.0176,0.0040</t>
-  </si>
-  <si>
-    <t>0.4498,0.4120,0.1535,0.0020</t>
-  </si>
-  <si>
-    <t>0.0016,0.0069,0.9907,0.0060</t>
-  </si>
-  <si>
-    <t>0.0267,0.8855,0.1160,0.0001</t>
-  </si>
-  <si>
-    <t>0.5169,0.4997,0.0526,0.0136</t>
-  </si>
-  <si>
-    <t>0.2004,0.3325,0.6296,0.0053</t>
-  </si>
-  <si>
-    <t>0.6628,0.4605,0.0105,0.0016</t>
-  </si>
-  <si>
-    <t>0.0431,0.9306,0.0778,0.0017</t>
-  </si>
-  <si>
-    <t>0.0188,0.8548,0.1496,0.0567</t>
-  </si>
-  <si>
-    <t>0.0648,0.0274,0.8759,0.0580</t>
-  </si>
-  <si>
-    <t>0.0348,0.6157,0.7763,0.0377</t>
-  </si>
-  <si>
-    <t>0.0172,0.0022,0.9686,0.0290</t>
-  </si>
-  <si>
-    <t>0.0162,0.3237,0.8706,0.0053</t>
-  </si>
-  <si>
-    <t>0.0374,0.8791,0.1426,0.0015</t>
-  </si>
-  <si>
-    <t>0.0220,0.0307,0.9535,0.0085</t>
-  </si>
-  <si>
-    <t>0.0494,0.5749,0.0035,0.7312</t>
-  </si>
-  <si>
-    <t>0.0068,0.9644,0.0081,0.0393</t>
-  </si>
-  <si>
-    <t>0.0089,0.9359,0.1209,0.0476</t>
-  </si>
-  <si>
-    <t>0.0006,0.9890,0.0036,0.0140</t>
-  </si>
-  <si>
-    <t>0.0058,0.0976,0.9297,0.0393</t>
-  </si>
-  <si>
-    <t>0.0043,0.4615,0.9598,0.0014</t>
-  </si>
-  <si>
-    <t>0.0225,0.0157,0.9553,0.0081</t>
-  </si>
-  <si>
-    <t>0.1192,0.0028,0.9486,0.0017</t>
-  </si>
-  <si>
-    <t>0.0048,0.0024,0.9839,0.0119</t>
-  </si>
-  <si>
-    <t>0.0243,0.0326,0.9361,0.0027</t>
-  </si>
-  <si>
-    <t>0.9678,0.0251,0.0013,0.0017</t>
-  </si>
-  <si>
-    <t>0.9160,0.0404,0.0504,0.0026</t>
-  </si>
-  <si>
-    <t>0.9570,0.0401,0.0037,0.0027</t>
-  </si>
-  <si>
-    <t>0.0477,0.2068,0.9184,0.0027</t>
-  </si>
-  <si>
-    <t>0.9868,0.0081,0.0008,0.0008</t>
-  </si>
-  <si>
-    <t>0.9879,0.0090,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9161,0.1158,0.0069,0.0015</t>
-  </si>
-  <si>
-    <t>0.0014,0.9354,0.7236,0.0005</t>
-  </si>
-  <si>
-    <t>0.0219,0.0180,0.9793,0.0011</t>
-  </si>
-  <si>
-    <t>0.0236,0.1826,0.9231,0.0145</t>
-  </si>
-  <si>
-    <t>0.0006,0.8053,0.9782,0.0001</t>
-  </si>
-  <si>
-    <t>0.0018,0.0033,0.9923,0.0055</t>
-  </si>
-  <si>
-    <t>0.1123,0.8958,0.0185,0.0017</t>
-  </si>
-  <si>
-    <t>0.0881,0.9153,0.0259,0.0009</t>
-  </si>
-  <si>
-    <t>0.7954,0.0445,0.2298,0.0007</t>
-  </si>
-  <si>
-    <t>0.6897,0.0955,0.2769,0.0040</t>
-  </si>
-  <si>
-    <t>0.0029,0.0617,0.9888,0.0011</t>
-  </si>
-  <si>
-    <t>0.0013,0.9108,0.7537,0.0002</t>
-  </si>
-  <si>
-    <t>0.0048,0.9165,0.6350,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.9967,0.0374,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.8902,0.9542,0.0002</t>
-  </si>
-  <si>
-    <t>0.0407,0.0023,0.1047,0.9230</t>
-  </si>
-  <si>
-    <t>0.0016,0.0038,0.0003,0.9990</t>
-  </si>
-  <si>
-    <t>0.0027,0.0011,0.0004,0.9987</t>
-  </si>
-  <si>
-    <t>0.0079,0.0238,0.0014,0.9946</t>
-  </si>
-  <si>
-    <t>0.0639,0.0009,0.0094,0.9589</t>
-  </si>
-  <si>
-    <t>0.0154,0.0092,0.0031,0.9917</t>
-  </si>
-  <si>
-    <t>0.0026,0.9350,0.6685,0.0032</t>
-  </si>
-  <si>
-    <t>0.0102,0.5294,0.9166,0.0038</t>
-  </si>
-  <si>
-    <t>0.0096,0.8086,0.4548,0.0123</t>
-  </si>
-  <si>
-    <t>0.0068,0.5336,0.9253,0.0048</t>
-  </si>
-  <si>
-    <t>0.0003,0.9448,0.9015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0064,0.6601,0.8891,0.0013</t>
-  </si>
-  <si>
-    <t>0.9880,0.0075,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.9838,0.0170,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9961,0.0032,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9928,0.0029,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9902,0.0040,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9945,0.0027,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9955,0.0017,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9935,0.0024,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9958,0.0007,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9877,0.0047,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9967,0.0005,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9949,0.0021,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9975,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0008,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9967,0.0006,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0084,0.0099,0.9853,0.0035</t>
-  </si>
-  <si>
-    <t>0.1981,0.0077,0.8611,0.0113</t>
-  </si>
-  <si>
-    <t>0.7573,0.0133,0.1271,0.0757</t>
-  </si>
-  <si>
-    <t>0.2271,0.0174,0.8401,0.0032</t>
-  </si>
-  <si>
-    <t>0.0365,0.9631,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.0152,0.9820,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.1194,0.8655,0.0009,0.0052</t>
-  </si>
-  <si>
-    <t>0.5220,0.6448,0.0022,0.0012</t>
-  </si>
-  <si>
-    <t>0.1149,0.8981,0.0051,0.0033</t>
-  </si>
-  <si>
-    <t>0.0102,0.9836,0.0034,0.0001</t>
-  </si>
-  <si>
-    <t>0.7511,0.4111,0.0031,0.0006</t>
-  </si>
-  <si>
-    <t>0.3937,0.3502,0.2310,0.0044</t>
-  </si>
-  <si>
-    <t>0.1546,0.0322,0.8064,0.0021</t>
-  </si>
-  <si>
-    <t>0.0978,0.7263,0.0190,0.2294</t>
-  </si>
-  <si>
-    <t>0.4631,0.3744,0.2412,0.0070</t>
-  </si>
-  <si>
-    <t>0.0487,0.2969,0.0131,0.8969</t>
-  </si>
-  <si>
-    <t>0.0003,0.9937,0.0005,0.0151</t>
-  </si>
-  <si>
-    <t>0.0295,0.9283,0.0809,0.0154</t>
-  </si>
-  <si>
-    <t>0.0013,0.9818,0.0016,0.0381</t>
-  </si>
-  <si>
-    <t>0.0019,0.9649,0.6410,0.0022</t>
-  </si>
-  <si>
-    <t>0.0820,0.9298,0.0226,0.0003</t>
-  </si>
-  <si>
-    <t>0.5676,0.5223,0.0195,0.0009</t>
-  </si>
-  <si>
-    <t>0.7998,0.2454,0.0157,0.0022</t>
-  </si>
-  <si>
-    <t>0.9930,0.0067,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9807,0.0073,0.0008,0.0020</t>
-  </si>
-  <si>
-    <t>0.9928,0.0013,0.0005,0.0014</t>
-  </si>
-  <si>
-    <t>0.9916,0.0019,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9914,0.0011,0.0001,0.0018</t>
-  </si>
-  <si>
-    <t>0.9846,0.0042,0.0098,0.0009</t>
-  </si>
-  <si>
-    <t>0.9856,0.0048,0.0008,0.0020</t>
-  </si>
-  <si>
-    <t>0.9935,0.0011,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.0165,0.7506,0.7735,0.0038</t>
-  </si>
-  <si>
-    <t>0.0024,0.8652,0.7342,0.0004</t>
-  </si>
-  <si>
-    <t>0.0077,0.0139,0.9854,0.0007</t>
-  </si>
-  <si>
-    <t>0.0207,0.1100,0.9145,0.0019</t>
-  </si>
-  <si>
-    <t>0.9428,0.0119,0.0168,0.0070</t>
-  </si>
-  <si>
-    <t>0.4318,0.0790,0.5861,0.0487</t>
-  </si>
-  <si>
-    <t>0.5260,0.0078,0.7290,0.0049</t>
-  </si>
-  <si>
-    <t>0.3359,0.1356,0.1989,0.2991</t>
-  </si>
-  <si>
-    <t>0.2242,0.0026,0.0035,0.9020</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.0016,0.9992</t>
-  </si>
-  <si>
-    <t>0.0144,0.0501,0.0040,0.9890</t>
-  </si>
-  <si>
-    <t>0.0136,0.0011,0.0021,0.9930</t>
-  </si>
-  <si>
-    <t>0.0042,0.8843,0.7097,0.0055</t>
-  </si>
-  <si>
-    <t>0.9887,0.0043,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.1533,0.8107,0.0009,0.0096</t>
-  </si>
-  <si>
-    <t>0.9842,0.0019,0.0004,0.0045</t>
-  </si>
-  <si>
-    <t>0.7337,0.3447,0.0117,0.0054</t>
-  </si>
-  <si>
-    <t>0.9798,0.0026,0.0011,0.0067</t>
-  </si>
-  <si>
-    <t>0.3244,0.0168,0.0339,0.7534</t>
-  </si>
-  <si>
-    <t>0.9351,0.0411,0.0106,0.0097</t>
-  </si>
-  <si>
-    <t>0.0060,0.2279,0.9383,0.0227</t>
-  </si>
-  <si>
-    <t>0.7417,0.0002,0.0028,0.3439</t>
-  </si>
-  <si>
-    <t>0.9699,0.0023,0.0198,0.0037</t>
-  </si>
-  <si>
-    <t>0.5476,0.3764,0.1040,0.0040</t>
-  </si>
-  <si>
-    <t>0.5299,0.2358,0.0037,0.1302</t>
-  </si>
-  <si>
-    <t>0.9141,0.0557,0.0331,0.0009</t>
-  </si>
-  <si>
-    <t>0.2592,0.6793,0.0491,0.0546</t>
-  </si>
-  <si>
-    <t>0.7248,0.4051,0.0055,0.0016</t>
-  </si>
-  <si>
-    <t>0.8948,0.0581,0.0509,0.0026</t>
-  </si>
-  <si>
-    <t>0.9890,0.0027,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9883,0.0054,0.0020,0.0007</t>
-  </si>
-  <si>
-    <t>0.9975,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9824,0.0017,0.0009,0.0078</t>
-  </si>
-  <si>
-    <t>0.9856,0.0056,0.0018,0.0013</t>
-  </si>
-  <si>
-    <t>0.9924,0.0025,0.0005,0.0006</t>
-  </si>
-  <si>
-    <t>0.9948,0.0015,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9948,0.0005,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.4164,0.7046,0.0044,0.0021</t>
-  </si>
-  <si>
-    <t>0.8614,0.2271,0.0077,0.0003</t>
-  </si>
-  <si>
-    <t>0.6150,0.5052,0.0123,0.0018</t>
-  </si>
-  <si>
-    <t>0.3012,0.0812,0.7523,0.0062</t>
-  </si>
-  <si>
-    <t>0.9593,0.0443,0.0018,0.0014</t>
-  </si>
-  <si>
-    <t>0.9263,0.0594,0.0197,0.0038</t>
-  </si>
-  <si>
-    <t>0.9886,0.0031,0.0005,0.0015</t>
-  </si>
-  <si>
-    <t>0.9837,0.0062,0.0026,0.0012</t>
-  </si>
-  <si>
-    <t>0.0126,0.0068,0.9898,0.0030</t>
-  </si>
-  <si>
-    <t>0.9340,0.0671,0.0137,0.0028</t>
-  </si>
-  <si>
-    <t>0.0005,0.0009,0.9952,0.0099</t>
-  </si>
-  <si>
-    <t>0.0627,0.2248,0.8618,0.0083</t>
-  </si>
-  <si>
-    <t>0.0128,0.0022,0.9840,0.0108</t>
-  </si>
-  <si>
-    <t>0.0058,0.1738,0.9747,0.0015</t>
-  </si>
-  <si>
-    <t>0.0622,0.0297,0.9302,0.0027</t>
-  </si>
-  <si>
-    <t>0.0061,0.0009,0.9915,0.0039</t>
-  </si>
-  <si>
-    <t>0.0041,0.0135,0.9863,0.0018</t>
-  </si>
-  <si>
-    <t>0.2267,0.0365,0.7691,0.0026</t>
-  </si>
-  <si>
-    <t>0.1583,0.0211,0.8666,0.0029</t>
-  </si>
-  <si>
-    <t>0.3202,0.0786,0.6758,0.0134</t>
-  </si>
-  <si>
-    <t>0.2421,0.1973,0.4896,0.0029</t>
-  </si>
-  <si>
-    <t>0.5919,0.1508,0.2805,0.0078</t>
-  </si>
-  <si>
-    <t>0.5847,0.0768,0.4340,0.0082</t>
-  </si>
-  <si>
-    <t>0.4181,0.2676,0.2298,0.0962</t>
-  </si>
-  <si>
-    <t>0.0787,0.0886,0.8486,0.0045</t>
-  </si>
-  <si>
-    <t>0.6718,0.4670,0.0037,0.0004</t>
-  </si>
-  <si>
-    <t>0.5113,0.6681,0.0029,0.0007</t>
-  </si>
-  <si>
-    <t>0.8946,0.1371,0.0083,0.0014</t>
-  </si>
-  <si>
-    <t>0.9753,0.0202,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.9562,0.0708,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.7497,0.0249,0.2050,0.0348</t>
-  </si>
-  <si>
-    <t>0.8318,0.0649,0.1038,0.0083</t>
-  </si>
-  <si>
-    <t>0.5857,0.2601,0.1855,0.0466</t>
-  </si>
-  <si>
-    <t>0.6106,0.0175,0.5426,0.0100</t>
-  </si>
-  <si>
-    <t>0.4286,0.0647,0.6086,0.0647</t>
-  </si>
-  <si>
-    <t>0.0329,0.0237,0.9469,0.0113</t>
-  </si>
-  <si>
-    <t>0.0424,0.1488,0.7346,0.1757</t>
-  </si>
-  <si>
-    <t>0.0150,0.1311,0.9384,0.0094</t>
-  </si>
-  <si>
-    <t>0.0446,0.1747,0.8617,0.0419</t>
-  </si>
-  <si>
-    <t>0.0347,0.1052,0.9134,0.0028</t>
-  </si>
-  <si>
-    <t>0.9906,0.0029,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9868,0.0054,0.0009,0.0014</t>
-  </si>
-  <si>
-    <t>0.9938,0.0012,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9918,0.0053,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9966,0.0014,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9899,0.0059,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9967,0.0011,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9954,0.0016,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0484,0.0235,0.9563,0.0027</t>
-  </si>
-  <si>
-    <t>0.1019,0.6790,0.2919,0.0032</t>
-  </si>
-  <si>
-    <t>0.8694,0.0782,0.0294,0.0171</t>
-  </si>
-  <si>
-    <t>0.0669,0.0615,0.8905,0.0110</t>
-  </si>
-  <si>
-    <t>0.0003,0.0017,0.9969,0.0023</t>
-  </si>
-  <si>
-    <t>0.0156,0.0971,0.9163,0.0010</t>
-  </si>
-  <si>
-    <t>0.0008,0.0039,0.9973,0.0004</t>
-  </si>
-  <si>
-    <t>0.0388,0.1499,0.7939,0.0074</t>
-  </si>
-  <si>
-    <t>0.0048,0.0045,0.9843,0.0100</t>
-  </si>
-  <si>
-    <t>0.0184,0.0172,0.9594,0.0086</t>
-  </si>
-  <si>
-    <t>0.0494,0.0595,0.8465,0.0047</t>
-  </si>
-  <si>
-    <t>0.7955,0.0045,0.1660,0.0380</t>
-  </si>
-  <si>
-    <t>0.4669,0.0281,0.6162,0.0055</t>
-  </si>
-  <si>
-    <t>0.7148,0.0078,0.4471,0.0063</t>
-  </si>
-  <si>
-    <t>0.9781,0.0246,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.9897,0.0035,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9912,0.0058,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.9916,0.0023,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9955,0.0012,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9926,0.0039,0.0007,0.0004</t>
-  </si>
-  <si>
-    <t>0.9931,0.0023,0.0003,0.0008</t>
-  </si>
-  <si>
-    <t>0.9863,0.0044,0.0003,0.0017</t>
-  </si>
-  <si>
-    <t>0.0070,0.5776,0.7709,0.0004</t>
-  </si>
-  <si>
-    <t>0.0026,0.0115,0.9901,0.0023</t>
-  </si>
-  <si>
-    <t>0.0100,0.0091,0.9694,0.0135</t>
-  </si>
-  <si>
-    <t>0.0767,0.0114,0.9261,0.0008</t>
-  </si>
-  <si>
-    <t>0.0102,0.0057,0.9805,0.0088</t>
-  </si>
-  <si>
-    <t>0.0614,0.0136,0.6941,0.4009</t>
-  </si>
-  <si>
-    <t>0.0328,0.0042,0.9630,0.0112</t>
-  </si>
-  <si>
-    <t>0.0036,0.0269,0.9413,0.0874</t>
-  </si>
-  <si>
-    <t>0.8450,0.0007,0.0021,0.2121</t>
-  </si>
-  <si>
-    <t>0.0024,0.0034,0.0004,0.9986</t>
-  </si>
-  <si>
-    <t>0.0180,0.0218,0.0020,0.9894</t>
-  </si>
-  <si>
-    <t>0.0058,0.0001,0.0013,0.9968</t>
-  </si>
-  <si>
-    <t>0.0033,0.0002,0.0003,0.9986</t>
-  </si>
-  <si>
-    <t>0.7596,0.0246,0.0723,0.1483</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,1,1</t>
+  </si>
+  <si>
+    <t>0.9458,0.0192,0.0073,0.0086</t>
+  </si>
+  <si>
+    <t>0.0090,0.0003,0.0002,0.9976</t>
+  </si>
+  <si>
+    <t>0.7880,0.0108,0.0056,0.2044</t>
+  </si>
+  <si>
+    <t>0.2148,0.0016,0.0112,0.8716</t>
+  </si>
+  <si>
+    <t>0.9977,0.0017,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0016,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9883,0.0054,0.0029,0.0008</t>
+  </si>
+  <si>
+    <t>0.9962,0.0010,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9882,0.0108,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9945,0.0065,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0004,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9963,0.0017,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.7701,0.0700,0.1448,0.0208</t>
+  </si>
+  <si>
+    <t>0.0955,0.0331,0.9250,0.0022</t>
+  </si>
+  <si>
+    <t>0.1337,0.0449,0.8183,0.0010</t>
+  </si>
+  <si>
+    <t>0.3227,0.0163,0.7855,0.0107</t>
+  </si>
+  <si>
+    <t>0.9201,0.0219,0.0534,0.0054</t>
+  </si>
+  <si>
+    <t>0.0216,0.9682,0.0015,0.0022</t>
+  </si>
+  <si>
+    <t>0.0765,0.9314,0.0112,0.0007</t>
+  </si>
+  <si>
+    <t>0.6821,0.4416,0.0072,0.0023</t>
+  </si>
+  <si>
+    <t>0.1498,0.9019,0.0023,0.0009</t>
+  </si>
+  <si>
+    <t>0.0303,0.9676,0.0038,0.0005</t>
+  </si>
+  <si>
+    <t>0.2209,0.0348,0.6078,0.2265</t>
+  </si>
+  <si>
+    <t>0.6902,0.0110,0.1793,0.1124</t>
+  </si>
+  <si>
+    <t>0.0354,0.0129,0.9522,0.0037</t>
+  </si>
+  <si>
+    <t>0.5053,0.0024,0.5962,0.0190</t>
+  </si>
+  <si>
+    <t>0.1556,0.0042,0.9198,0.0040</t>
+  </si>
+  <si>
+    <t>0.0359,0.0018,0.9721,0.0049</t>
+  </si>
+  <si>
+    <t>0.0009,0.0011,0.9869,0.0446</t>
+  </si>
+  <si>
+    <t>0.8099,0.2558,0.0105,0.0019</t>
+  </si>
+  <si>
+    <t>0.2521,0.3719,0.3734,0.0058</t>
+  </si>
+  <si>
+    <t>0.0021,0.0044,0.9939,0.0028</t>
+  </si>
+  <si>
+    <t>0.0559,0.6538,0.4232,0.0007</t>
+  </si>
+  <si>
+    <t>0.8189,0.1685,0.0195,0.0142</t>
+  </si>
+  <si>
+    <t>0.6375,0.3714,0.0408,0.0025</t>
+  </si>
+  <si>
+    <t>0.7617,0.3456,0.0076,0.0010</t>
+  </si>
+  <si>
+    <t>0.1098,0.8022,0.3010,0.0172</t>
+  </si>
+  <si>
+    <t>0.0879,0.1721,0.7019,0.0634</t>
+  </si>
+  <si>
+    <t>0.0035,0.0054,0.9593,0.1061</t>
+  </si>
+  <si>
+    <t>0.0704,0.2302,0.7699,0.0329</t>
+  </si>
+  <si>
+    <t>0.1252,0.0153,0.8849,0.0186</t>
+  </si>
+  <si>
+    <t>0.1340,0.0734,0.8086,0.0019</t>
+  </si>
+  <si>
+    <t>0.0195,0.8564,0.3085,0.0010</t>
+  </si>
+  <si>
+    <t>0.0052,0.0085,0.9859,0.0055</t>
+  </si>
+  <si>
+    <t>0.1715,0.6648,0.0502,0.3597</t>
+  </si>
+  <si>
+    <t>0.0107,0.9560,0.0176,0.0311</t>
+  </si>
+  <si>
+    <t>0.0081,0.9607,0.0740,0.0090</t>
+  </si>
+  <si>
+    <t>0.0044,0.9701,0.0105,0.0236</t>
+  </si>
+  <si>
+    <t>0.0146,0.0236,0.9633,0.0113</t>
+  </si>
+  <si>
+    <t>0.0047,0.5842,0.9609,0.0005</t>
+  </si>
+  <si>
+    <t>0.0336,0.0100,0.9601,0.0059</t>
+  </si>
+  <si>
+    <t>0.0303,0.0059,0.9705,0.0017</t>
+  </si>
+  <si>
+    <t>0.0100,0.0094,0.9837,0.0034</t>
+  </si>
+  <si>
+    <t>0.0127,0.0103,0.9806,0.0003</t>
+  </si>
+  <si>
+    <t>0.9468,0.0685,0.0081,0.0012</t>
+  </si>
+  <si>
+    <t>0.9267,0.0429,0.0188,0.0058</t>
+  </si>
+  <si>
+    <t>0.9672,0.0202,0.0050,0.0026</t>
+  </si>
+  <si>
+    <t>0.0976,0.0387,0.9257,0.0065</t>
+  </si>
+  <si>
+    <t>0.9927,0.0012,0.0001,0.0012</t>
+  </si>
+  <si>
+    <t>0.9861,0.0103,0.0017,0.0006</t>
+  </si>
+  <si>
+    <t>0.9937,0.0022,0.0012,0.0005</t>
+  </si>
+  <si>
+    <t>0.0109,0.6481,0.8734,0.0016</t>
+  </si>
+  <si>
+    <t>0.0182,0.1197,0.9475,0.0057</t>
+  </si>
+  <si>
+    <t>0.0136,0.0217,0.9567,0.0170</t>
+  </si>
+  <si>
+    <t>0.0009,0.8640,0.9570,0.0005</t>
+  </si>
+  <si>
+    <t>0.0022,0.0045,0.9923,0.0038</t>
+  </si>
+  <si>
+    <t>0.1355,0.5969,0.4218,0.0050</t>
+  </si>
+  <si>
+    <t>0.0415,0.9532,0.0025,0.0015</t>
+  </si>
+  <si>
+    <t>0.9564,0.0147,0.0407,0.0013</t>
+  </si>
+  <si>
+    <t>0.8567,0.0634,0.0945,0.0067</t>
+  </si>
+  <si>
+    <t>0.0066,0.0669,0.9854,0.0016</t>
+  </si>
+  <si>
+    <t>0.0024,0.9249,0.6461,0.0015</t>
+  </si>
+  <si>
+    <t>0.0035,0.9059,0.7357,0.0006</t>
+  </si>
+  <si>
+    <t>0.0027,0.9505,0.6563,0.0012</t>
+  </si>
+  <si>
+    <t>0.0016,0.8347,0.9613,0.0006</t>
+  </si>
+  <si>
+    <t>0.0095,0.0000,0.0132,0.9849</t>
+  </si>
+  <si>
+    <t>0.0007,0.0254,0.0009,0.9988</t>
+  </si>
+  <si>
+    <t>0.0086,0.0063,0.0014,0.9952</t>
+  </si>
+  <si>
+    <t>0.0111,0.0088,0.0016,0.9941</t>
+  </si>
+  <si>
+    <t>0.0509,0.0168,0.0084,0.9695</t>
+  </si>
+  <si>
+    <t>0.0094,0.0135,0.0009,0.9949</t>
+  </si>
+  <si>
+    <t>0.0022,0.9040,0.8480,0.0005</t>
+  </si>
+  <si>
+    <t>0.0047,0.4198,0.9552,0.0008</t>
+  </si>
+  <si>
+    <t>0.0525,0.7586,0.2917,0.0214</t>
+  </si>
+  <si>
+    <t>0.0019,0.5034,0.9748,0.0008</t>
+  </si>
+  <si>
+    <t>0.0033,0.9475,0.5383,0.0006</t>
+  </si>
+  <si>
+    <t>0.0518,0.6960,0.4317,0.0200</t>
+  </si>
+  <si>
+    <t>0.9852,0.0083,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9877,0.0059,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9607,0.0427,0.0039,0.0013</t>
+  </si>
+  <si>
+    <t>0.9960,0.0005,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.9978,0.0007,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9942,0.0017,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9920,0.0067,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9942,0.0018,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9919,0.0004,0.0000,0.0030</t>
+  </si>
+  <si>
+    <t>0.9969,0.0009,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9959,0.0018,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9967,0.0004,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9953,0.0013,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9960,0.0019,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9961,0.0008,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0043,0.9859,0.0152</t>
+  </si>
+  <si>
+    <t>0.0783,0.0155,0.9132,0.0056</t>
+  </si>
+  <si>
+    <t>0.5861,0.0078,0.0905,0.2810</t>
+  </si>
+  <si>
+    <t>0.0206,0.0029,0.9791,0.0030</t>
+  </si>
+  <si>
+    <t>0.0668,0.9442,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0313,0.9644,0.0051,0.0002</t>
+  </si>
+  <si>
+    <t>0.1606,0.8647,0.0026,0.0019</t>
+  </si>
+  <si>
+    <t>0.2153,0.8453,0.0029,0.0013</t>
+  </si>
+  <si>
+    <t>0.0298,0.9667,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.0122,0.9782,0.0026,0.0005</t>
+  </si>
+  <si>
+    <t>0.0579,0.9328,0.0099,0.0011</t>
+  </si>
+  <si>
+    <t>0.3578,0.2661,0.3385,0.0044</t>
+  </si>
+  <si>
+    <t>0.2789,0.0144,0.8149,0.0149</t>
+  </si>
+  <si>
+    <t>0.4238,0.1623,0.4034,0.1522</t>
+  </si>
+  <si>
+    <t>0.6905,0.0741,0.3391,0.0182</t>
+  </si>
+  <si>
+    <t>0.5478,0.0773,0.1704,0.2566</t>
+  </si>
+  <si>
+    <t>0.0109,0.9504,0.0123,0.0429</t>
+  </si>
+  <si>
+    <t>0.0021,0.9873,0.0090,0.0022</t>
+  </si>
+  <si>
+    <t>0.0249,0.8911,0.0259,0.1215</t>
+  </si>
+  <si>
+    <t>0.0059,0.9185,0.7436,0.0016</t>
+  </si>
+  <si>
+    <t>0.1338,0.8810,0.0361,0.0004</t>
+  </si>
+  <si>
+    <t>0.4688,0.6551,0.0075,0.0002</t>
+  </si>
+  <si>
+    <t>0.4872,0.6200,0.0093,0.0031</t>
+  </si>
+  <si>
+    <t>0.9941,0.0028,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9905,0.0044,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9916,0.0010,0.0005,0.0024</t>
+  </si>
+  <si>
+    <t>0.9846,0.0097,0.0008,0.0011</t>
+  </si>
+  <si>
+    <t>0.9833,0.0025,0.0002,0.0046</t>
+  </si>
+  <si>
+    <t>0.9689,0.0106,0.0242,0.0016</t>
+  </si>
+  <si>
+    <t>0.9890,0.0013,0.0004,0.0038</t>
+  </si>
+  <si>
+    <t>0.9797,0.0067,0.0051,0.0024</t>
+  </si>
+  <si>
+    <t>0.0292,0.6125,0.8095,0.0086</t>
+  </si>
+  <si>
+    <t>0.0035,0.6529,0.9240,0.0008</t>
+  </si>
+  <si>
+    <t>0.0062,0.1493,0.9569,0.0011</t>
+  </si>
+  <si>
+    <t>0.0486,0.4745,0.6402,0.0186</t>
+  </si>
+  <si>
+    <t>0.8331,0.0275,0.0768,0.0441</t>
+  </si>
+  <si>
+    <t>0.1831,0.7103,0.0071,0.0775</t>
+  </si>
+  <si>
+    <t>0.3006,0.0034,0.8581,0.0075</t>
+  </si>
+  <si>
+    <t>0.5502,0.0240,0.6101,0.0063</t>
+  </si>
+  <si>
+    <t>0.1613,0.0046,0.0159,0.9140</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0007,0.9996</t>
+  </si>
+  <si>
+    <t>0.0036,0.0033,0.0005,0.9982</t>
+  </si>
+  <si>
+    <t>0.0068,0.0041,0.0008,0.9965</t>
+  </si>
+  <si>
+    <t>0.0054,0.4789,0.9111,0.0037</t>
+  </si>
+  <si>
+    <t>0.9546,0.0229,0.0052,0.0070</t>
+  </si>
+  <si>
+    <t>0.7536,0.3339,0.0179,0.0020</t>
+  </si>
+  <si>
+    <t>0.9830,0.0032,0.0011,0.0035</t>
+  </si>
+  <si>
+    <t>0.8379,0.2845,0.0046,0.0010</t>
+  </si>
+  <si>
+    <t>0.9808,0.0048,0.0025,0.0035</t>
+  </si>
+  <si>
+    <t>0.1266,0.0027,0.0011,0.9570</t>
+  </si>
+  <si>
+    <t>0.9673,0.0075,0.0043,0.0074</t>
+  </si>
+  <si>
+    <t>0.0033,0.1394,0.9326,0.0282</t>
+  </si>
+  <si>
+    <t>0.7941,0.0003,0.0026,0.2590</t>
+  </si>
+  <si>
+    <t>0.9074,0.0018,0.0044,0.0925</t>
+  </si>
+  <si>
+    <t>0.2448,0.8085,0.0141,0.0073</t>
+  </si>
+  <si>
+    <t>0.7285,0.2729,0.0282,0.0128</t>
+  </si>
+  <si>
+    <t>0.9039,0.1000,0.0118,0.0012</t>
+  </si>
+  <si>
+    <t>0.5219,0.5107,0.0251,0.0071</t>
+  </si>
+  <si>
+    <t>0.7497,0.1785,0.0962,0.0054</t>
+  </si>
+  <si>
+    <t>0.8447,0.1245,0.0462,0.0034</t>
+  </si>
+  <si>
+    <t>0.9953,0.0010,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9878,0.0052,0.0006,0.0011</t>
+  </si>
+  <si>
+    <t>0.9908,0.0027,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9882,0.0007,0.0010,0.0038</t>
+  </si>
+  <si>
+    <t>0.9902,0.0023,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9933,0.0022,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9861,0.0023,0.0009,0.0027</t>
+  </si>
+  <si>
+    <t>0.9885,0.0043,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.2076,0.8082,0.0041,0.0057</t>
+  </si>
+  <si>
+    <t>0.7502,0.3386,0.0167,0.0010</t>
+  </si>
+  <si>
+    <t>0.2494,0.8216,0.0096,0.0002</t>
+  </si>
+  <si>
+    <t>0.1244,0.2264,0.8132,0.0050</t>
+  </si>
+  <si>
+    <t>0.9501,0.0475,0.0019,0.0024</t>
+  </si>
+  <si>
+    <t>0.9719,0.0135,0.0029,0.0024</t>
+  </si>
+  <si>
+    <t>0.9862,0.0121,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9716,0.0246,0.0022,0.0013</t>
+  </si>
+  <si>
+    <t>0.0018,0.0372,0.9953,0.0006</t>
+  </si>
+  <si>
+    <t>0.9659,0.0261,0.0033,0.0016</t>
+  </si>
+  <si>
+    <t>0.0025,0.0306,0.9930,0.0001</t>
+  </si>
+  <si>
+    <t>0.0241,0.1166,0.9399,0.0072</t>
+  </si>
+  <si>
+    <t>0.0366,0.0030,0.9719,0.0057</t>
+  </si>
+  <si>
+    <t>0.0926,0.1017,0.8896,0.0040</t>
+  </si>
+  <si>
+    <t>0.0323,0.1411,0.8660,0.0142</t>
+  </si>
+  <si>
+    <t>0.0043,0.0017,0.9954,0.0001</t>
+  </si>
+  <si>
+    <t>0.0022,0.0071,0.9946,0.0006</t>
+  </si>
+  <si>
+    <t>0.3504,0.2833,0.4579,0.0301</t>
+  </si>
+  <si>
+    <t>0.3925,0.0356,0.6969,0.0037</t>
+  </si>
+  <si>
+    <t>0.4625,0.0574,0.6218,0.0084</t>
+  </si>
+  <si>
+    <t>0.1593,0.4244,0.4611,0.0068</t>
+  </si>
+  <si>
+    <t>0.2321,0.0966,0.7057,0.0064</t>
+  </si>
+  <si>
+    <t>0.6307,0.1505,0.2321,0.0086</t>
+  </si>
+  <si>
+    <t>0.3877,0.2754,0.3709,0.0214</t>
+  </si>
+  <si>
+    <t>0.4951,0.0148,0.7003,0.0044</t>
+  </si>
+  <si>
+    <t>0.7666,0.2881,0.0151,0.0008</t>
+  </si>
+  <si>
+    <t>0.8818,0.2289,0.0024,0.0004</t>
+  </si>
+  <si>
+    <t>0.9562,0.0435,0.0067,0.0015</t>
+  </si>
+  <si>
+    <t>0.9219,0.1073,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9758,0.0335,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.6497,0.2973,0.0832,0.0164</t>
+  </si>
+  <si>
+    <t>0.5474,0.0210,0.5607,0.0218</t>
+  </si>
+  <si>
+    <t>0.4078,0.0972,0.0370,0.5028</t>
+  </si>
+  <si>
+    <t>0.6415,0.0084,0.2861,0.0670</t>
+  </si>
+  <si>
+    <t>0.7189,0.0856,0.2155,0.0111</t>
+  </si>
+  <si>
+    <t>0.0390,0.0061,0.9628,0.0114</t>
+  </si>
+  <si>
+    <t>0.1569,0.0713,0.6575,0.1673</t>
+  </si>
+  <si>
+    <t>0.0261,0.0736,0.8760,0.0586</t>
+  </si>
+  <si>
+    <t>0.0904,0.0367,0.8824,0.0186</t>
+  </si>
+  <si>
+    <t>0.0625,0.5659,0.4678,0.0239</t>
+  </si>
+  <si>
+    <t>0.9864,0.0024,0.0002,0.0025</t>
+  </si>
+  <si>
+    <t>0.9782,0.0256,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.9853,0.0100,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9776,0.0226,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9885,0.0031,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.9904,0.0019,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9922,0.0080,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9892,0.0064,0.0008,0.0008</t>
+  </si>
+  <si>
+    <t>0.2574,0.0083,0.8293,0.0161</t>
+  </si>
+  <si>
+    <t>0.3132,0.1851,0.5782,0.0124</t>
+  </si>
+  <si>
+    <t>0.8855,0.0290,0.0387,0.0281</t>
+  </si>
+  <si>
+    <t>0.0170,0.0310,0.9653,0.0021</t>
+  </si>
+  <si>
+    <t>0.0067,0.0173,0.9784,0.0112</t>
+  </si>
+  <si>
+    <t>0.0497,0.0977,0.8789,0.0041</t>
+  </si>
+  <si>
+    <t>0.0016,0.0032,0.9927,0.0040</t>
+  </si>
+  <si>
+    <t>0.2047,0.0871,0.7089,0.0142</t>
+  </si>
+  <si>
+    <t>0.0034,0.0052,0.9854,0.0076</t>
+  </si>
+  <si>
+    <t>0.0078,0.0122,0.9847,0.0020</t>
+  </si>
+  <si>
+    <t>0.2916,0.0371,0.7565,0.0103</t>
+  </si>
+  <si>
+    <t>0.8618,0.0124,0.1718,0.0050</t>
+  </si>
+  <si>
+    <t>0.6092,0.0059,0.4213,0.0411</t>
+  </si>
+  <si>
+    <t>0.8157,0.0383,0.1041,0.0364</t>
+  </si>
+  <si>
+    <t>0.9883,0.0044,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9914,0.0062,0.0008,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0019,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9848,0.0164,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9958,0.0010,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9940,0.0018,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9927,0.0068,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9956,0.0019,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.0029,0.7268,0.8368,0.0003</t>
+  </si>
+  <si>
+    <t>0.0052,0.0353,0.9862,0.0011</t>
+  </si>
+  <si>
+    <t>0.0072,0.0077,0.9884,0.0020</t>
+  </si>
+  <si>
+    <t>0.0263,0.0316,0.9276,0.0021</t>
+  </si>
+  <si>
+    <t>0.0051,0.0205,0.9842,0.0018</t>
+  </si>
+  <si>
+    <t>0.1400,0.0580,0.0722,0.8551</t>
+  </si>
+  <si>
+    <t>0.1133,0.0135,0.9002,0.0070</t>
+  </si>
+  <si>
+    <t>0.0010,0.0027,0.8862,0.5759</t>
+  </si>
+  <si>
+    <t>0.8330,0.0008,0.0071,0.1920</t>
+  </si>
+  <si>
+    <t>0.0033,0.0564,0.0021,0.9949</t>
+  </si>
+  <si>
+    <t>0.0740,0.0019,0.0043,0.9677</t>
+  </si>
+  <si>
+    <t>0.0047,0.0002,0.0002,0.9986</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.0004,0.9995</t>
+  </si>
+  <si>
+    <t>0.8150,0.0508,0.0326,0.0786</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,7 +1996,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,7 +2276,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,7 +2290,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,10 +2315,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,10 +2511,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2995,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3093,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,10 +3113,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3121,7 +3130,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3149,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3597,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3863,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3919,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,10 +3939,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4059,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4129,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,7 +4390,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4395,7 +4404,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4507,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4605,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4689,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4731,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4759,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,10 +4793,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,10 +4807,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,10 +4821,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4871,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5036,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5095,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>263</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,7 +5454,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
